--- a/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
+++ b/InputData/elec/CRbQ/Cap Retirements before Quantization.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Brazil/CRbQ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/elec/CRbQ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DE5F1B-F987-4945-BD5C-CF27A3164715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE91BBA-B4C5-7445-AF16-5E5C3F6544DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="14" r:id="rId1"/>
@@ -297,7 +297,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -377,6 +377,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-9.9978637043366805E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -436,7 +451,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="16" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="17">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -7765,28 +7780,28 @@
         <v>0</v>
       </c>
       <c r="B4" s="14">
-        <f>BCRBQ!B59</f>
-        <v>1500</v>
+        <f>0</f>
+        <v>0</v>
       </c>
       <c r="C4" s="14">
-        <f>BCRBQ!C59</f>
-        <v>1000</v>
+        <f>B4</f>
+        <v>0</v>
       </c>
       <c r="D4" s="14">
-        <f>BCRBQ!D59</f>
-        <v>500</v>
+        <f t="shared" ref="D4:G4" si="0">C4</f>
+        <v>0</v>
       </c>
       <c r="E4" s="14">
-        <f>BCRBQ!E59</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F4" s="14">
-        <f>BCRBQ!F59</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G4" s="14">
-        <f>BCRBQ!G59</f>
-        <v>1500</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>0</v>
